--- a/results/reports/year_2025_report.xlsx
+++ b/results/reports/year_2025_report.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R2"/>
+  <dimension ref="A1:T2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -505,30 +505,40 @@
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
+          <t>top_30_return_compounded</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>top_30_excess</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
           <t>decile_return_compounded</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>decile_excess</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>OMXS30_return</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>OMXC25_return</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>OMXH25_return</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>OSEBX_return</t>
         </is>
@@ -572,21 +582,27 @@
         <v>59.4</v>
       </c>
       <c r="M2" t="n">
+        <v>56.58</v>
+      </c>
+      <c r="N2" t="n">
+        <v>62.27</v>
+      </c>
+      <c r="O2" t="n">
         <v>42.79</v>
       </c>
-      <c r="N2" t="n">
+      <c r="P2" t="n">
         <v>48.48</v>
       </c>
-      <c r="O2" t="n">
+      <c r="Q2" t="n">
         <v>16.1</v>
       </c>
-      <c r="P2" t="n">
+      <c r="R2" t="n">
         <v>2.66</v>
       </c>
-      <c r="Q2" t="n">
+      <c r="S2" t="n">
         <v>32.15</v>
       </c>
-      <c r="R2" t="n">
+      <c r="T2" t="n">
         <v>18.44</v>
       </c>
     </row>
@@ -647,7 +663,7 @@
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="n">
-        <v>0.6875360832357208</v>
+        <v>0.6875360832357207</v>
       </c>
       <c r="E2" t="n">
         <v>3.6647</v>
@@ -707,7 +723,7 @@
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="n">
-        <v>0.6701615958337335</v>
+        <v>0.6701615958337332</v>
       </c>
       <c r="E5" t="n">
         <v>1.8539</v>
@@ -767,7 +783,7 @@
       </c>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="n">
-        <v>0.6646741675820408</v>
+        <v>0.6646741675820407</v>
       </c>
       <c r="E8" t="n">
         <v>-2.3659</v>
@@ -787,7 +803,7 @@
       </c>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="n">
-        <v>0.6631079006287958</v>
+        <v>0.6631079006287959</v>
       </c>
       <c r="E9" t="n">
         <v>1.1156</v>
@@ -887,7 +903,7 @@
       </c>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="n">
-        <v>0.6397480645383873</v>
+        <v>0.6397480645383874</v>
       </c>
       <c r="E14" t="n">
         <v>-4.0853</v>
@@ -1113,7 +1129,7 @@
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="n">
-        <v>0.6947074415083009</v>
+        <v>0.694707441508301</v>
       </c>
       <c r="E3" t="n">
         <v>5.4557</v>
@@ -1133,7 +1149,7 @@
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="n">
-        <v>0.6903016121227367</v>
+        <v>0.6903016121227366</v>
       </c>
       <c r="E4" t="n">
         <v>-0.9732</v>
@@ -1213,7 +1229,7 @@
       </c>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="n">
-        <v>0.6846915492997553</v>
+        <v>0.6846915492997552</v>
       </c>
       <c r="E8" t="n">
         <v>-1.0002</v>
@@ -1253,7 +1269,7 @@
       </c>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="n">
-        <v>0.6801230200758149</v>
+        <v>0.6801230200758152</v>
       </c>
       <c r="E10" t="n">
         <v>7.771</v>
@@ -1293,7 +1309,7 @@
       </c>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="n">
-        <v>0.675280109839774</v>
+        <v>0.6752801098397743</v>
       </c>
       <c r="E12" t="n">
         <v>1.4851</v>
@@ -1353,7 +1369,7 @@
       </c>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="n">
-        <v>0.6713468288206279</v>
+        <v>0.6713468288206278</v>
       </c>
       <c r="E15" t="n">
         <v>1.1952</v>
@@ -1413,7 +1429,7 @@
       </c>
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="n">
-        <v>0.664632061936217</v>
+        <v>0.6646320619362168</v>
       </c>
       <c r="E18" t="n">
         <v>-1.8897</v>
@@ -1539,7 +1555,7 @@
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="n">
-        <v>0.7233596613442391</v>
+        <v>0.723359661344239</v>
       </c>
       <c r="E2" t="n">
         <v>0.1975</v>
@@ -1559,7 +1575,7 @@
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="n">
-        <v>0.7111088478840222</v>
+        <v>0.7111088478840221</v>
       </c>
       <c r="E3" t="n">
         <v>4.0476</v>
@@ -1579,7 +1595,7 @@
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="n">
-        <v>0.7074481775230737</v>
+        <v>0.7074481775230739</v>
       </c>
       <c r="E4" t="n">
         <v>-2.8007</v>
@@ -1599,7 +1615,7 @@
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="n">
-        <v>0.705212293348477</v>
+        <v>0.7052122933484768</v>
       </c>
       <c r="E5" t="n">
         <v>1.7769</v>
@@ -1619,7 +1635,7 @@
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="n">
-        <v>0.7038600317616468</v>
+        <v>0.7038600317616467</v>
       </c>
       <c r="E6" t="n">
         <v>1.5326</v>
@@ -1719,7 +1735,7 @@
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="n">
-        <v>0.679895154933163</v>
+        <v>0.6798951549331629</v>
       </c>
       <c r="E11" t="n">
         <v>5.8818</v>
@@ -1759,7 +1775,7 @@
       </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="n">
-        <v>0.6786207105960886</v>
+        <v>0.6786207105960885</v>
       </c>
       <c r="E13" t="n">
         <v>-0.5013</v>
@@ -1779,7 +1795,7 @@
       </c>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="n">
-        <v>0.6756697132843869</v>
+        <v>0.6756697132843867</v>
       </c>
       <c r="E14" t="n">
         <v>9.968500000000001</v>
@@ -1859,7 +1875,7 @@
       </c>
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="n">
-        <v>0.6624540547763175</v>
+        <v>0.6624540547763174</v>
       </c>
       <c r="E18" t="n">
         <v>0.906</v>
@@ -1879,7 +1895,7 @@
       </c>
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="n">
-        <v>0.6602131181891043</v>
+        <v>0.6602131181891042</v>
       </c>
       <c r="E19" t="n">
         <v>6.5713</v>
@@ -1985,7 +2001,7 @@
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="n">
-        <v>0.7370024782616303</v>
+        <v>0.7370024782616305</v>
       </c>
       <c r="E2" t="n">
         <v>3.4188</v>
@@ -2005,7 +2021,7 @@
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="n">
-        <v>0.7246050068889744</v>
+        <v>0.7246050068889742</v>
       </c>
       <c r="E3" t="n">
         <v>2.7042</v>
@@ -2025,7 +2041,7 @@
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="n">
-        <v>0.723363264041016</v>
+        <v>0.7233632640410157</v>
       </c>
       <c r="E4" t="n">
         <v>2.1298</v>
@@ -2045,7 +2061,7 @@
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="n">
-        <v>0.7147341403095189</v>
+        <v>0.7147341403095188</v>
       </c>
       <c r="E5" t="n">
         <v>4.084</v>
@@ -2065,7 +2081,7 @@
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="n">
-        <v>0.7074704539151335</v>
+        <v>0.7074704539151336</v>
       </c>
       <c r="E6" t="n">
         <v>-0.7619</v>
@@ -2085,7 +2101,7 @@
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="n">
-        <v>0.6944111271512233</v>
+        <v>0.6944111271512234</v>
       </c>
       <c r="E7" t="n">
         <v>5.9743</v>
@@ -2105,7 +2121,7 @@
       </c>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="n">
-        <v>0.6900783392822956</v>
+        <v>0.6900783392822958</v>
       </c>
       <c r="E8" t="n">
         <v>2.3508</v>
@@ -2165,7 +2181,7 @@
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="n">
-        <v>0.6783721736500822</v>
+        <v>0.678372173650082</v>
       </c>
       <c r="E11" t="n">
         <v>-0.9852</v>
@@ -2245,7 +2261,7 @@
       </c>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="n">
-        <v>0.6653901131054404</v>
+        <v>0.6653901131054405</v>
       </c>
       <c r="E15" t="n">
         <v>-2.2697</v>
@@ -2285,7 +2301,7 @@
       </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="n">
-        <v>0.6625201100552145</v>
+        <v>0.6625201100552147</v>
       </c>
       <c r="E17" t="n">
         <v>-1.0515</v>
@@ -2365,7 +2381,7 @@
       </c>
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="n">
-        <v>0.6518234010500279</v>
+        <v>0.6518234010500281</v>
       </c>
       <c r="E21" t="n">
         <v>-1.2091</v>
@@ -2471,7 +2487,7 @@
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="n">
-        <v>0.7204812658691668</v>
+        <v>0.7204812658691669</v>
       </c>
       <c r="E4" t="n">
         <v>-0.6823</v>
@@ -2491,7 +2507,7 @@
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="n">
-        <v>0.7170458823503409</v>
+        <v>0.7170458823503408</v>
       </c>
       <c r="E5" t="n">
         <v>5.7278</v>
@@ -2511,7 +2527,7 @@
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="n">
-        <v>0.7150935300525467</v>
+        <v>0.7150935300525468</v>
       </c>
       <c r="E6" t="n">
         <v>4.8005</v>
@@ -2551,7 +2567,7 @@
       </c>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="n">
-        <v>0.6944565585637237</v>
+        <v>0.6944565585637236</v>
       </c>
       <c r="E8" t="n">
         <v>3.5</v>
@@ -2591,7 +2607,7 @@
       </c>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="n">
-        <v>0.6778121269643219</v>
+        <v>0.6778121269643218</v>
       </c>
       <c r="E10" t="n">
         <v>9.5608</v>
@@ -2651,7 +2667,7 @@
       </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="n">
-        <v>0.6706934986155896</v>
+        <v>0.6706934986155898</v>
       </c>
       <c r="E13" t="n">
         <v>7.5286</v>
@@ -2671,7 +2687,7 @@
       </c>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="n">
-        <v>0.6703971864264393</v>
+        <v>0.6703971864264395</v>
       </c>
       <c r="E14" t="n">
         <v>-0.7479</v>
@@ -2731,7 +2747,7 @@
       </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="n">
-        <v>0.6569403811723988</v>
+        <v>0.6569403811723989</v>
       </c>
       <c r="E17" t="n">
         <v>4.1774</v>
@@ -2751,7 +2767,7 @@
       </c>
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="n">
-        <v>0.6547390387261436</v>
+        <v>0.6547390387261437</v>
       </c>
       <c r="E18" t="n">
         <v>-0.0461</v>
@@ -2811,7 +2827,7 @@
       </c>
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="n">
-        <v>0.6513153568929689</v>
+        <v>0.6513153568929692</v>
       </c>
       <c r="E21" t="n">
         <v>3.5905</v>
@@ -2917,7 +2933,7 @@
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="n">
-        <v>0.7133153716439057</v>
+        <v>0.7133153716439058</v>
       </c>
       <c r="E4" t="n">
         <v>1.9169</v>
@@ -2997,7 +3013,7 @@
       </c>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="n">
-        <v>0.6977040463317842</v>
+        <v>0.6977040463317843</v>
       </c>
       <c r="E8" t="n">
         <v>-1.1335</v>
@@ -3137,7 +3153,7 @@
       </c>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="n">
-        <v>0.6797775055744272</v>
+        <v>0.6797775055744271</v>
       </c>
       <c r="E15" t="n">
         <v>9.993600000000001</v>
@@ -3277,7 +3293,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H13"/>
+  <dimension ref="A1:I13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3298,25 +3314,30 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>top_30_return</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>decile_return</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>OMXS30</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>OMXC25</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>OMXH25</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>OSEBX</t>
         </is>
@@ -3333,18 +3354,21 @@
         <v>10.95</v>
       </c>
       <c r="D2" t="n">
+        <v>8.57</v>
+      </c>
+      <c r="E2" t="n">
         <v>7.08</v>
       </c>
-      <c r="E2" t="n">
+      <c r="F2" t="n">
         <v>7.55</v>
       </c>
-      <c r="F2" t="n">
+      <c r="G2" t="n">
         <v>-0.21</v>
       </c>
-      <c r="G2" t="n">
+      <c r="H2" t="n">
         <v>5.9</v>
       </c>
-      <c r="H2" t="n">
+      <c r="I2" t="n">
         <v>6.34</v>
       </c>
     </row>
@@ -3359,18 +3383,21 @@
         <v>4.27</v>
       </c>
       <c r="D3" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="E3" t="n">
         <v>-0.26</v>
       </c>
-      <c r="E3" t="n">
+      <c r="F3" t="n">
         <v>2.03</v>
       </c>
-      <c r="F3" t="n">
+      <c r="G3" t="n">
         <v>4.41</v>
       </c>
-      <c r="G3" t="n">
+      <c r="H3" t="n">
         <v>3.26</v>
       </c>
-      <c r="H3" t="n">
+      <c r="I3" t="n">
         <v>-1.7</v>
       </c>
     </row>
@@ -3385,18 +3412,21 @@
         <v>3.31</v>
       </c>
       <c r="D4" t="n">
+        <v>3.43</v>
+      </c>
+      <c r="E4" t="n">
         <v>1.65</v>
       </c>
-      <c r="E4" t="n">
+      <c r="F4" t="n">
         <v>-8.460000000000001</v>
       </c>
-      <c r="F4" t="n">
+      <c r="G4" t="n">
         <v>-9.949999999999999</v>
       </c>
-      <c r="G4" t="n">
+      <c r="H4" t="n">
         <v>-4.54</v>
       </c>
-      <c r="H4" t="n">
+      <c r="I4" t="n">
         <v>1.8</v>
       </c>
     </row>
@@ -3411,18 +3441,21 @@
         <v>2.55</v>
       </c>
       <c r="D5" t="n">
+        <v>4.39</v>
+      </c>
+      <c r="E5" t="n">
         <v>3.54</v>
       </c>
-      <c r="E5" t="n">
+      <c r="F5" t="n">
         <v>-2.41</v>
       </c>
-      <c r="F5" t="n">
+      <c r="G5" t="n">
         <v>-0.6899999999999999</v>
       </c>
-      <c r="G5" t="n">
+      <c r="H5" t="n">
         <v>-0.19</v>
       </c>
-      <c r="H5" t="n">
+      <c r="I5" t="n">
         <v>-1.94</v>
       </c>
     </row>
@@ -3437,18 +3470,21 @@
         <v>0.98</v>
       </c>
       <c r="D6" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="E6" t="n">
         <v>1.23</v>
       </c>
-      <c r="E6" t="n">
+      <c r="F6" t="n">
         <v>2.55</v>
       </c>
-      <c r="F6" t="n">
+      <c r="G6" t="n">
         <v>6.37</v>
       </c>
-      <c r="G6" t="n">
+      <c r="H6" t="n">
         <v>5.2</v>
       </c>
-      <c r="H6" t="n">
+      <c r="I6" t="n">
         <v>5.01</v>
       </c>
     </row>
@@ -3463,18 +3499,21 @@
         <v>3.39</v>
       </c>
       <c r="D7" t="n">
+        <v>3.92</v>
+      </c>
+      <c r="E7" t="n">
         <v>3.42</v>
       </c>
-      <c r="E7" t="n">
+      <c r="F7" t="n">
         <v>-0.1</v>
       </c>
-      <c r="F7" t="n">
+      <c r="G7" t="n">
         <v>-3.12</v>
       </c>
-      <c r="G7" t="n">
+      <c r="H7" t="n">
         <v>1.06</v>
       </c>
-      <c r="H7" t="n">
+      <c r="I7" t="n">
         <v>3.82</v>
       </c>
     </row>
@@ -3489,18 +3528,21 @@
         <v>1.94</v>
       </c>
       <c r="D8" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="E8" t="n">
         <v>2.74</v>
       </c>
-      <c r="E8" t="n">
+      <c r="F8" t="n">
         <v>3.47</v>
       </c>
-      <c r="F8" t="n">
+      <c r="G8" t="n">
         <v>-2.42</v>
       </c>
-      <c r="G8" t="n">
+      <c r="H8" t="n">
         <v>1.6</v>
       </c>
-      <c r="H8" t="n">
+      <c r="I8" t="n">
         <v>0.24</v>
       </c>
     </row>
@@ -3515,18 +3557,21 @@
         <v>2.96</v>
       </c>
       <c r="D9" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="E9" t="n">
         <v>1.39</v>
       </c>
-      <c r="E9" t="n">
+      <c r="F9" t="n">
         <v>1.77</v>
       </c>
-      <c r="F9" t="n">
+      <c r="G9" t="n">
         <v>0.09</v>
       </c>
-      <c r="G9" t="n">
+      <c r="H9" t="n">
         <v>1.36</v>
       </c>
-      <c r="H9" t="n">
+      <c r="I9" t="n">
         <v>1.31</v>
       </c>
     </row>
@@ -3541,18 +3586,21 @@
         <v>2.82</v>
       </c>
       <c r="D10" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="E10" t="n">
         <v>3.11</v>
       </c>
-      <c r="E10" t="n">
+      <c r="F10" t="n">
         <v>1.41</v>
       </c>
-      <c r="F10" t="n">
+      <c r="G10" t="n">
         <v>-2.3</v>
       </c>
-      <c r="G10" t="n">
+      <c r="H10" t="n">
         <v>1.89</v>
       </c>
-      <c r="H10" t="n">
+      <c r="I10" t="n">
         <v>-0.12</v>
       </c>
     </row>
@@ -3567,18 +3615,21 @@
         <v>2.03</v>
       </c>
       <c r="D11" t="n">
+        <v>3.01</v>
+      </c>
+      <c r="E11" t="n">
         <v>2.85</v>
       </c>
-      <c r="E11" t="n">
+      <c r="F11" t="n">
         <v>3.92</v>
       </c>
-      <c r="F11" t="n">
+      <c r="G11" t="n">
         <v>3.48</v>
       </c>
-      <c r="G11" t="n">
+      <c r="H11" t="n">
         <v>9.27</v>
       </c>
-      <c r="H11" t="n">
+      <c r="I11" t="n">
         <v>-1.99</v>
       </c>
     </row>
@@ -3593,18 +3644,21 @@
         <v>5.49</v>
       </c>
       <c r="D12" t="n">
+        <v>5.52</v>
+      </c>
+      <c r="E12" t="n">
         <v>4.92</v>
       </c>
-      <c r="E12" t="n">
+      <c r="F12" t="n">
         <v>0.75</v>
       </c>
-      <c r="F12" t="n">
+      <c r="G12" t="n">
         <v>3.66</v>
       </c>
-      <c r="G12" t="n">
+      <c r="H12" t="n">
         <v>-0.92</v>
       </c>
-      <c r="H12" t="n">
+      <c r="I12" t="n">
         <v>-0.13</v>
       </c>
     </row>
@@ -3619,18 +3673,21 @@
         <v>3.41</v>
       </c>
       <c r="D13" t="n">
+        <v>4.89</v>
+      </c>
+      <c r="E13" t="n">
         <v>4.7</v>
       </c>
-      <c r="E13" t="n">
+      <c r="F13" t="n">
         <v>3.41</v>
       </c>
-      <c r="F13" t="n">
+      <c r="G13" t="n">
         <v>4.44</v>
       </c>
-      <c r="G13" t="n">
+      <c r="H13" t="n">
         <v>5.03</v>
       </c>
-      <c r="H13" t="n">
+      <c r="I13" t="n">
         <v>4.85</v>
       </c>
     </row>
@@ -3917,7 +3974,7 @@
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="n">
-        <v>0.6907078756300602</v>
+        <v>0.6907078756300601</v>
       </c>
       <c r="E2" t="n">
         <v>-2.2857</v>
@@ -3957,7 +4014,7 @@
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="n">
-        <v>0.6864480914417734</v>
+        <v>0.6864480914417735</v>
       </c>
       <c r="E4" t="n">
         <v>9.935600000000001</v>
@@ -3977,7 +4034,7 @@
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="n">
-        <v>0.6820195257230013</v>
+        <v>0.6820195257230012</v>
       </c>
       <c r="E5" t="n">
         <v>2.0116</v>
@@ -4057,7 +4114,7 @@
       </c>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="n">
-        <v>0.665409613107775</v>
+        <v>0.6654096131077749</v>
       </c>
       <c r="E9" t="n">
         <v>11.2505</v>
@@ -4077,7 +4134,7 @@
       </c>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="n">
-        <v>0.6552388494269175</v>
+        <v>0.6552388494269173</v>
       </c>
       <c r="E10" t="n">
         <v>4.1601</v>
@@ -4157,7 +4214,7 @@
       </c>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="n">
-        <v>0.6471948049488639</v>
+        <v>0.6471948049488638</v>
       </c>
       <c r="E14" t="n">
         <v>8.460900000000001</v>
@@ -4237,7 +4294,7 @@
       </c>
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="n">
-        <v>0.6397866441184236</v>
+        <v>0.6397866441184237</v>
       </c>
       <c r="E18" t="n">
         <v>16.5219</v>
@@ -4257,7 +4314,7 @@
       </c>
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="n">
-        <v>0.6326125580117242</v>
+        <v>0.6326125580117243</v>
       </c>
       <c r="E19" t="n">
         <v>10.9175</v>
@@ -4383,7 +4440,7 @@
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="n">
-        <v>0.6866577630591126</v>
+        <v>0.6866577630591125</v>
       </c>
       <c r="E3" t="n">
         <v>38.3065</v>
@@ -4403,7 +4460,7 @@
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="n">
-        <v>0.6865555947975924</v>
+        <v>0.6865555947975926</v>
       </c>
       <c r="E4" t="n">
         <v>3.8656</v>
@@ -4443,7 +4500,7 @@
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="n">
-        <v>0.6594563669309034</v>
+        <v>0.6594563669309033</v>
       </c>
       <c r="E6" t="n">
         <v>6.9864</v>
@@ -4583,7 +4640,7 @@
       </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="n">
-        <v>0.6358124156685681</v>
+        <v>0.6358124156685682</v>
       </c>
       <c r="E13" t="n">
         <v>-15.165</v>
@@ -4809,7 +4866,7 @@
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="n">
-        <v>0.7047074658664088</v>
+        <v>0.7047074658664089</v>
       </c>
       <c r="E2" t="n">
         <v>-4.6538</v>
@@ -4889,7 +4946,7 @@
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="n">
-        <v>0.6914557268233851</v>
+        <v>0.6914557268233853</v>
       </c>
       <c r="E6" t="n">
         <v>-5.1886</v>
@@ -4909,7 +4966,7 @@
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="n">
-        <v>0.6778711143295354</v>
+        <v>0.6778711143295355</v>
       </c>
       <c r="E7" t="n">
         <v>4.5638</v>
@@ -4969,7 +5026,7 @@
       </c>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="n">
-        <v>0.6589479529112865</v>
+        <v>0.6589479529112866</v>
       </c>
       <c r="E10" t="n">
         <v>1.7932</v>
@@ -5029,7 +5086,7 @@
       </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="n">
-        <v>0.6505325204110862</v>
+        <v>0.6505325204110863</v>
       </c>
       <c r="E13" t="n">
         <v>0.9101</v>
@@ -5335,7 +5392,7 @@
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="n">
-        <v>0.6319572382210125</v>
+        <v>0.6319572382210126</v>
       </c>
       <c r="E6" t="n">
         <v>-0.6682</v>
@@ -5355,7 +5412,7 @@
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="n">
-        <v>0.6314692206724727</v>
+        <v>0.6314692206724728</v>
       </c>
       <c r="E7" t="n">
         <v>-0.4167</v>
@@ -5375,7 +5432,7 @@
       </c>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="n">
-        <v>0.6228173626516744</v>
+        <v>0.6228173626516743</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -5415,7 +5472,7 @@
       </c>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="n">
-        <v>0.6073876695898907</v>
+        <v>0.6073876695898905</v>
       </c>
       <c r="E10" t="n">
         <v>2.5784</v>
@@ -5435,7 +5492,7 @@
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="n">
-        <v>0.6066224245077949</v>
+        <v>0.6066224245077948</v>
       </c>
       <c r="E11" t="n">
         <v>-9.8187</v>
@@ -5455,7 +5512,7 @@
       </c>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="n">
-        <v>0.6028857763693424</v>
+        <v>0.6028857763693425</v>
       </c>
       <c r="E12" t="n">
         <v>9.9664</v>
@@ -5555,7 +5612,7 @@
       </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="n">
-        <v>0.5947126037885103</v>
+        <v>0.5947126037885102</v>
       </c>
       <c r="E17" t="n">
         <v>0.1707</v>
@@ -5595,7 +5652,7 @@
       </c>
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="n">
-        <v>0.591501340248373</v>
+        <v>0.5915013402483729</v>
       </c>
       <c r="E19" t="n">
         <v>6.9048</v>
@@ -5635,7 +5692,7 @@
       </c>
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="n">
-        <v>0.587777668239274</v>
+        <v>0.5877776682392739</v>
       </c>
       <c r="E21" t="n">
         <v>7.9252</v>
@@ -5721,7 +5778,7 @@
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="n">
-        <v>0.6903986078631412</v>
+        <v>0.6903986078631413</v>
       </c>
       <c r="E3" t="n">
         <v>-0.6925</v>
@@ -5761,7 +5818,7 @@
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="n">
-        <v>0.6878400022501114</v>
+        <v>0.6878400022501112</v>
       </c>
       <c r="E5" t="n">
         <v>2.3965</v>
@@ -5801,7 +5858,7 @@
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="n">
-        <v>0.6795822582740405</v>
+        <v>0.6795822582740404</v>
       </c>
       <c r="E7" t="n">
         <v>-0.2733</v>
@@ -5901,7 +5958,7 @@
       </c>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="n">
-        <v>0.6601250699587707</v>
+        <v>0.6601250699587708</v>
       </c>
       <c r="E12" t="n">
         <v>-1.5867</v>
@@ -5961,7 +6018,7 @@
       </c>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="n">
-        <v>0.6520296687377409</v>
+        <v>0.652029668737741</v>
       </c>
       <c r="E15" t="n">
         <v>-0.6006</v>
@@ -6001,7 +6058,7 @@
       </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="n">
-        <v>0.6414820319365038</v>
+        <v>0.6414820319365035</v>
       </c>
       <c r="E17" t="n">
         <v>4.7215</v>
@@ -6247,7 +6304,7 @@
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="n">
-        <v>0.6781738316735823</v>
+        <v>0.6781738316735825</v>
       </c>
       <c r="E7" t="n">
         <v>11.3978</v>
@@ -6267,7 +6324,7 @@
       </c>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="n">
-        <v>0.6760664369476516</v>
+        <v>0.6760664369476515</v>
       </c>
       <c r="E8" t="n">
         <v>6.0248</v>
@@ -6327,7 +6384,7 @@
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="n">
-        <v>0.6690311967477426</v>
+        <v>0.6690311967477425</v>
       </c>
       <c r="E11" t="n">
         <v>4.3963</v>
@@ -6347,7 +6404,7 @@
       </c>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="n">
-        <v>0.6607383237830173</v>
+        <v>0.6607383237830174</v>
       </c>
       <c r="E12" t="n">
         <v>-4.3495</v>
@@ -6427,7 +6484,7 @@
       </c>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="n">
-        <v>0.6465423741729015</v>
+        <v>0.6465423741729013</v>
       </c>
       <c r="E16" t="n">
         <v>2.1279</v>
@@ -6507,7 +6564,7 @@
       </c>
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="n">
-        <v>0.6333605972870848</v>
+        <v>0.6333605972870847</v>
       </c>
       <c r="E20" t="n">
         <v>2.5054</v>

--- a/results/reports/year_2025_report.xlsx
+++ b/results/reports/year_2025_report.xlsx
@@ -663,7 +663,7 @@
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="n">
-        <v>0.6875360832357207</v>
+        <v>0.6875360832357208</v>
       </c>
       <c r="E2" t="n">
         <v>3.6647</v>
@@ -703,7 +703,7 @@
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="n">
-        <v>0.6712839000241079</v>
+        <v>0.6712839000241076</v>
       </c>
       <c r="E4" t="n">
         <v>1.3393</v>
@@ -723,7 +723,7 @@
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="n">
-        <v>0.6701615958337332</v>
+        <v>0.6701615958337334</v>
       </c>
       <c r="E5" t="n">
         <v>1.8539</v>
@@ -743,7 +743,7 @@
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="n">
-        <v>0.6673468961933114</v>
+        <v>0.6673468961933113</v>
       </c>
       <c r="E6" t="n">
         <v>5.3073</v>
@@ -763,7 +763,7 @@
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="n">
-        <v>0.6663407181068977</v>
+        <v>0.6663407181068974</v>
       </c>
       <c r="E7" t="n">
         <v>4.4389</v>
@@ -783,7 +783,7 @@
       </c>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="n">
-        <v>0.6646741675820407</v>
+        <v>0.6646741675820408</v>
       </c>
       <c r="E8" t="n">
         <v>-2.3659</v>
@@ -843,7 +843,7 @@
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="n">
-        <v>0.6523310838129955</v>
+        <v>0.6523310838129958</v>
       </c>
       <c r="E11" t="n">
         <v>1.8162</v>
@@ -943,7 +943,7 @@
       </c>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="n">
-        <v>0.6378868356641381</v>
+        <v>0.637886835664138</v>
       </c>
       <c r="E16" t="n">
         <v>-2.5071</v>
@@ -1043,7 +1043,7 @@
       </c>
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="n">
-        <v>0.6330345015291134</v>
+        <v>0.6330345015291133</v>
       </c>
       <c r="E21" t="n">
         <v>2.487</v>
@@ -1129,7 +1129,7 @@
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="n">
-        <v>0.694707441508301</v>
+        <v>0.6947074415083009</v>
       </c>
       <c r="E3" t="n">
         <v>5.4557</v>
@@ -1149,7 +1149,7 @@
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="n">
-        <v>0.6903016121227366</v>
+        <v>0.6903016121227367</v>
       </c>
       <c r="E4" t="n">
         <v>-0.9732</v>
@@ -1169,7 +1169,7 @@
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="n">
-        <v>0.6888858395213004</v>
+        <v>0.6888858395213003</v>
       </c>
       <c r="E5" t="n">
         <v>5.6635</v>
@@ -1189,7 +1189,7 @@
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="n">
-        <v>0.6849214272028695</v>
+        <v>0.6849214272028693</v>
       </c>
       <c r="E6" t="n">
         <v>7.0655</v>
@@ -1269,7 +1269,7 @@
       </c>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="n">
-        <v>0.6801230200758152</v>
+        <v>0.6801230200758149</v>
       </c>
       <c r="E10" t="n">
         <v>7.771</v>
@@ -1309,7 +1309,7 @@
       </c>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="n">
-        <v>0.6752801098397743</v>
+        <v>0.675280109839774</v>
       </c>
       <c r="E12" t="n">
         <v>1.4851</v>
@@ -1409,7 +1409,7 @@
       </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="n">
-        <v>0.6662441592969668</v>
+        <v>0.6662441592969667</v>
       </c>
       <c r="E17" t="n">
         <v>6.7254</v>
@@ -1429,7 +1429,7 @@
       </c>
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="n">
-        <v>0.6646320619362168</v>
+        <v>0.664632061936217</v>
       </c>
       <c r="E18" t="n">
         <v>-1.8897</v>
@@ -1555,7 +1555,7 @@
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="n">
-        <v>0.723359661344239</v>
+        <v>0.7233596613442391</v>
       </c>
       <c r="E2" t="n">
         <v>0.1975</v>
@@ -1635,7 +1635,7 @@
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="n">
-        <v>0.7038600317616467</v>
+        <v>0.7038600317616468</v>
       </c>
       <c r="E6" t="n">
         <v>1.5326</v>
@@ -1735,7 +1735,7 @@
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="n">
-        <v>0.6798951549331629</v>
+        <v>0.679895154933163</v>
       </c>
       <c r="E11" t="n">
         <v>5.8818</v>
@@ -1755,7 +1755,7 @@
       </c>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="n">
-        <v>0.6791674564727265</v>
+        <v>0.6791674564727262</v>
       </c>
       <c r="E12" t="n">
         <v>-0.8383</v>
@@ -1795,7 +1795,7 @@
       </c>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="n">
-        <v>0.6756697132843867</v>
+        <v>0.6756697132843869</v>
       </c>
       <c r="E14" t="n">
         <v>9.968500000000001</v>
@@ -1835,7 +1835,7 @@
       </c>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="n">
-        <v>0.6734037796373257</v>
+        <v>0.6734037796373255</v>
       </c>
       <c r="E16" t="n">
         <v>1.3919</v>
@@ -2001,7 +2001,7 @@
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="n">
-        <v>0.7370024782616305</v>
+        <v>0.7370024782616303</v>
       </c>
       <c r="E2" t="n">
         <v>3.4188</v>
@@ -2021,7 +2021,7 @@
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="n">
-        <v>0.7246050068889742</v>
+        <v>0.7246050068889744</v>
       </c>
       <c r="E3" t="n">
         <v>2.7042</v>
@@ -2041,7 +2041,7 @@
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="n">
-        <v>0.7233632640410157</v>
+        <v>0.723363264041016</v>
       </c>
       <c r="E4" t="n">
         <v>2.1298</v>
@@ -2121,7 +2121,7 @@
       </c>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="n">
-        <v>0.6900783392822958</v>
+        <v>0.6900783392822956</v>
       </c>
       <c r="E8" t="n">
         <v>2.3508</v>
@@ -2321,7 +2321,7 @@
       </c>
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="n">
-        <v>0.6614319896766523</v>
+        <v>0.6614319896766522</v>
       </c>
       <c r="E18" t="n">
         <v>-4.5343</v>
@@ -2361,7 +2361,7 @@
       </c>
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="n">
-        <v>0.6526320580713201</v>
+        <v>0.65263205807132</v>
       </c>
       <c r="E20" t="n">
         <v>7.4008</v>
@@ -2381,7 +2381,7 @@
       </c>
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="n">
-        <v>0.6518234010500281</v>
+        <v>0.6518234010500279</v>
       </c>
       <c r="E21" t="n">
         <v>-1.2091</v>
@@ -2487,7 +2487,7 @@
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="n">
-        <v>0.7204812658691669</v>
+        <v>0.7204812658691668</v>
       </c>
       <c r="E4" t="n">
         <v>-0.6823</v>
@@ -2507,7 +2507,7 @@
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="n">
-        <v>0.7170458823503408</v>
+        <v>0.7170458823503409</v>
       </c>
       <c r="E5" t="n">
         <v>5.7278</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="n">
-        <v>0.7150935300525468</v>
+        <v>0.7150935300525467</v>
       </c>
       <c r="E6" t="n">
         <v>4.8005</v>
@@ -2567,7 +2567,7 @@
       </c>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="n">
-        <v>0.6944565585637236</v>
+        <v>0.6944565585637237</v>
       </c>
       <c r="E8" t="n">
         <v>3.5</v>
@@ -2667,7 +2667,7 @@
       </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="n">
-        <v>0.6706934986155898</v>
+        <v>0.6706934986155896</v>
       </c>
       <c r="E13" t="n">
         <v>7.5286</v>
@@ -2687,7 +2687,7 @@
       </c>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="n">
-        <v>0.6703971864264395</v>
+        <v>0.6703971864264393</v>
       </c>
       <c r="E14" t="n">
         <v>-0.7479</v>
@@ -2767,7 +2767,7 @@
       </c>
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="n">
-        <v>0.6547390387261437</v>
+        <v>0.6547390387261436</v>
       </c>
       <c r="E18" t="n">
         <v>-0.0461</v>
@@ -2893,7 +2893,7 @@
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="n">
-        <v>0.7176055642200199</v>
+        <v>0.7176055642200196</v>
       </c>
       <c r="E2" t="n">
         <v>33.9015</v>
@@ -2933,7 +2933,7 @@
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="n">
-        <v>0.7133153716439058</v>
+        <v>0.7133153716439057</v>
       </c>
       <c r="E4" t="n">
         <v>1.9169</v>
@@ -2973,7 +2973,7 @@
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="n">
-        <v>0.7060841701307461</v>
+        <v>0.706084170130746</v>
       </c>
       <c r="E6" t="n">
         <v>0.9369</v>
@@ -3013,7 +3013,7 @@
       </c>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="n">
-        <v>0.6977040463317843</v>
+        <v>0.6977040463317842</v>
       </c>
       <c r="E8" t="n">
         <v>-1.1335</v>
@@ -3053,7 +3053,7 @@
       </c>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="n">
-        <v>0.6893060851466436</v>
+        <v>0.6893060851466434</v>
       </c>
       <c r="E10" t="n">
         <v>-0.525</v>
@@ -3073,7 +3073,7 @@
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="n">
-        <v>0.6848484911963304</v>
+        <v>0.6848484911963305</v>
       </c>
       <c r="E11" t="n">
         <v>-0.0452</v>
@@ -3133,7 +3133,7 @@
       </c>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="n">
-        <v>0.6814124588426834</v>
+        <v>0.6814124588426835</v>
       </c>
       <c r="E14" t="n">
         <v>5.3862</v>
@@ -3173,7 +3173,7 @@
       </c>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="n">
-        <v>0.6760887698859531</v>
+        <v>0.6760887698859532</v>
       </c>
       <c r="E16" t="n">
         <v>1.6172</v>
@@ -3213,7 +3213,7 @@
       </c>
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="n">
-        <v>0.6570733568741677</v>
+        <v>0.6570733568741679</v>
       </c>
       <c r="E18" t="n">
         <v>-1.0246</v>
@@ -4014,7 +4014,7 @@
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="n">
-        <v>0.6864480914417735</v>
+        <v>0.6864480914417734</v>
       </c>
       <c r="E4" t="n">
         <v>9.935600000000001</v>
@@ -4034,7 +4034,7 @@
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="n">
-        <v>0.6820195257230012</v>
+        <v>0.6820195257230013</v>
       </c>
       <c r="E5" t="n">
         <v>2.0116</v>
@@ -4054,7 +4054,7 @@
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="n">
-        <v>0.6798697679798187</v>
+        <v>0.6798697679798188</v>
       </c>
       <c r="E6" t="n">
         <v>21.2401</v>
@@ -4154,7 +4154,7 @@
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="n">
-        <v>0.654856944370016</v>
+        <v>0.6548569443700161</v>
       </c>
       <c r="E11" t="n">
         <v>4.0462</v>
@@ -4214,7 +4214,7 @@
       </c>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="n">
-        <v>0.6471948049488638</v>
+        <v>0.6471948049488639</v>
       </c>
       <c r="E14" t="n">
         <v>8.460900000000001</v>
@@ -4294,7 +4294,7 @@
       </c>
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="n">
-        <v>0.6397866441184237</v>
+        <v>0.6397866441184236</v>
       </c>
       <c r="E18" t="n">
         <v>16.5219</v>
@@ -4314,7 +4314,7 @@
       </c>
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="n">
-        <v>0.6326125580117243</v>
+        <v>0.6326125580117242</v>
       </c>
       <c r="E19" t="n">
         <v>10.9175</v>
@@ -4420,7 +4420,7 @@
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="n">
-        <v>0.7040821243272047</v>
+        <v>0.7040821243272046</v>
       </c>
       <c r="E2" t="n">
         <v>2.4669</v>
@@ -4440,7 +4440,7 @@
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="n">
-        <v>0.6866577630591125</v>
+        <v>0.6866577630591126</v>
       </c>
       <c r="E3" t="n">
         <v>38.3065</v>
@@ -4500,7 +4500,7 @@
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="n">
-        <v>0.6594563669309033</v>
+        <v>0.6594563669309034</v>
       </c>
       <c r="E6" t="n">
         <v>6.9864</v>
@@ -4540,7 +4540,7 @@
       </c>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="n">
-        <v>0.6566949923743384</v>
+        <v>0.6566949923743383</v>
       </c>
       <c r="E8" t="n">
         <v>62.8931</v>
@@ -4640,7 +4640,7 @@
       </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="n">
-        <v>0.6358124156685682</v>
+        <v>0.6358124156685681</v>
       </c>
       <c r="E13" t="n">
         <v>-15.165</v>
@@ -4700,7 +4700,7 @@
       </c>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="n">
-        <v>0.6268374266188511</v>
+        <v>0.6268374266188512</v>
       </c>
       <c r="E16" t="n">
         <v>7.2094</v>
@@ -4740,7 +4740,7 @@
       </c>
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="n">
-        <v>0.6248748298440018</v>
+        <v>0.6248748298440017</v>
       </c>
       <c r="E18" t="n">
         <v>5.3394</v>
@@ -4866,7 +4866,7 @@
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="n">
-        <v>0.7047074658664089</v>
+        <v>0.7047074658664088</v>
       </c>
       <c r="E2" t="n">
         <v>-4.6538</v>
@@ -4946,7 +4946,7 @@
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="n">
-        <v>0.6914557268233853</v>
+        <v>0.6914557268233851</v>
       </c>
       <c r="E6" t="n">
         <v>-5.1886</v>
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="n">
-        <v>0.6589479529112866</v>
+        <v>0.6589479529112865</v>
       </c>
       <c r="E10" t="n">
         <v>1.7932</v>
@@ -5106,7 +5106,7 @@
       </c>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="n">
-        <v>0.6483105966431375</v>
+        <v>0.6483105966431377</v>
       </c>
       <c r="E14" t="n">
         <v>3.1898</v>
@@ -5226,7 +5226,7 @@
       </c>
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="n">
-        <v>0.6371534233746219</v>
+        <v>0.637153423374622</v>
       </c>
       <c r="E20" t="n">
         <v>-1.4619</v>
@@ -5332,7 +5332,7 @@
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="n">
-        <v>0.6533953493539555</v>
+        <v>0.6533953493539554</v>
       </c>
       <c r="E3" t="n">
         <v>5.4789</v>
@@ -5392,7 +5392,7 @@
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="n">
-        <v>0.6319572382210126</v>
+        <v>0.6319572382210125</v>
       </c>
       <c r="E6" t="n">
         <v>-0.6682</v>
@@ -5512,7 +5512,7 @@
       </c>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="n">
-        <v>0.6028857763693425</v>
+        <v>0.6028857763693424</v>
       </c>
       <c r="E12" t="n">
         <v>9.9664</v>
@@ -5532,7 +5532,7 @@
       </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="n">
-        <v>0.6016327875074282</v>
+        <v>0.6016327875074283</v>
       </c>
       <c r="E13" t="n">
         <v>1.964</v>
@@ -5652,7 +5652,7 @@
       </c>
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="n">
-        <v>0.5915013402483729</v>
+        <v>0.591501340248373</v>
       </c>
       <c r="E19" t="n">
         <v>6.9048</v>
@@ -5672,7 +5672,7 @@
       </c>
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="n">
-        <v>0.5914780163126112</v>
+        <v>0.591478016312611</v>
       </c>
       <c r="E20" t="n">
         <v>-1.5368</v>
@@ -5818,7 +5818,7 @@
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="n">
-        <v>0.6878400022501112</v>
+        <v>0.6878400022501114</v>
       </c>
       <c r="E5" t="n">
         <v>2.3965</v>
@@ -5858,7 +5858,7 @@
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="n">
-        <v>0.6795822582740404</v>
+        <v>0.6795822582740405</v>
       </c>
       <c r="E7" t="n">
         <v>-0.2733</v>
@@ -5898,7 +5898,7 @@
       </c>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="n">
-        <v>0.6638300685362605</v>
+        <v>0.6638300685362606</v>
       </c>
       <c r="E9" t="n">
         <v>1.1662</v>
@@ -6204,7 +6204,7 @@
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="n">
-        <v>0.7293514701845991</v>
+        <v>0.7293514701845994</v>
       </c>
       <c r="E2" t="n">
         <v>-0.398</v>
@@ -6264,7 +6264,7 @@
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="n">
-        <v>0.6858376006561984</v>
+        <v>0.6858376006561986</v>
       </c>
       <c r="E5" t="n">
         <v>3.9569</v>
@@ -6284,7 +6284,7 @@
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="n">
-        <v>0.6798931704401913</v>
+        <v>0.6798931704401915</v>
       </c>
       <c r="E6" t="n">
         <v>7.4709</v>
@@ -6324,7 +6324,7 @@
       </c>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="n">
-        <v>0.6760664369476515</v>
+        <v>0.6760664369476516</v>
       </c>
       <c r="E8" t="n">
         <v>6.0248</v>
@@ -6384,7 +6384,7 @@
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="n">
-        <v>0.6690311967477425</v>
+        <v>0.6690311967477426</v>
       </c>
       <c r="E11" t="n">
         <v>4.3963</v>
@@ -6404,7 +6404,7 @@
       </c>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="n">
-        <v>0.6607383237830174</v>
+        <v>0.6607383237830176</v>
       </c>
       <c r="E12" t="n">
         <v>-4.3495</v>
@@ -6504,7 +6504,7 @@
       </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="n">
-        <v>0.643661470735545</v>
+        <v>0.6436614707355449</v>
       </c>
       <c r="E17" t="n">
         <v>9.394399999999999</v>
@@ -6584,7 +6584,7 @@
       </c>
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="n">
-        <v>0.6332113548552343</v>
+        <v>0.6332113548552342</v>
       </c>
       <c r="E21" t="n">
         <v>2.2785</v>

--- a/results/reports/year_2025_report.xlsx
+++ b/results/reports/year_2025_report.xlsx
@@ -683,7 +683,7 @@
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="n">
-        <v>0.6862307672472809</v>
+        <v>0.686230767247281</v>
       </c>
       <c r="E3" t="n">
         <v>4.0767</v>
@@ -703,7 +703,7 @@
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="n">
-        <v>0.6712839000241076</v>
+        <v>0.6712839000241079</v>
       </c>
       <c r="E4" t="n">
         <v>1.3393</v>
@@ -723,7 +723,7 @@
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="n">
-        <v>0.6701615958337334</v>
+        <v>0.6701615958337335</v>
       </c>
       <c r="E5" t="n">
         <v>1.8539</v>
@@ -743,7 +743,7 @@
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="n">
-        <v>0.6673468961933113</v>
+        <v>0.6673468961933114</v>
       </c>
       <c r="E6" t="n">
         <v>5.3073</v>
@@ -843,7 +843,7 @@
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="n">
-        <v>0.6523310838129958</v>
+        <v>0.6523310838129955</v>
       </c>
       <c r="E11" t="n">
         <v>1.8162</v>
@@ -903,7 +903,7 @@
       </c>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="n">
-        <v>0.6397480645383874</v>
+        <v>0.6397480645383873</v>
       </c>
       <c r="E14" t="n">
         <v>-4.0853</v>
@@ -923,7 +923,7 @@
       </c>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="n">
-        <v>0.6389839872772085</v>
+        <v>0.6389839872772086</v>
       </c>
       <c r="E15" t="n">
         <v>8.7927</v>
@@ -943,7 +943,7 @@
       </c>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="n">
-        <v>0.637886835664138</v>
+        <v>0.6378868356641381</v>
       </c>
       <c r="E16" t="n">
         <v>-2.5071</v>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="n">
-        <v>0.6365870406856959</v>
+        <v>0.6365870406856958</v>
       </c>
       <c r="E19" t="n">
         <v>-0.4867</v>
@@ -1043,7 +1043,7 @@
       </c>
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="n">
-        <v>0.6330345015291133</v>
+        <v>0.6330345015291134</v>
       </c>
       <c r="E21" t="n">
         <v>2.487</v>
@@ -1149,7 +1149,7 @@
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="n">
-        <v>0.6903016121227367</v>
+        <v>0.6903016121227366</v>
       </c>
       <c r="E4" t="n">
         <v>-0.9732</v>
@@ -1189,7 +1189,7 @@
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="n">
-        <v>0.6849214272028693</v>
+        <v>0.6849214272028695</v>
       </c>
       <c r="E6" t="n">
         <v>7.0655</v>
@@ -1209,7 +1209,7 @@
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="n">
-        <v>0.6847606339207717</v>
+        <v>0.6847606339207718</v>
       </c>
       <c r="E7" t="n">
         <v>6.9553</v>
@@ -1229,7 +1229,7 @@
       </c>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="n">
-        <v>0.6846915492997552</v>
+        <v>0.6846915492997553</v>
       </c>
       <c r="E8" t="n">
         <v>-1.0002</v>
@@ -1249,7 +1249,7 @@
       </c>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="n">
-        <v>0.6817809580811215</v>
+        <v>0.6817809580811216</v>
       </c>
       <c r="E9" t="n">
         <v>-0.7212</v>
@@ -1269,7 +1269,7 @@
       </c>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="n">
-        <v>0.6801230200758149</v>
+        <v>0.6801230200758152</v>
       </c>
       <c r="E10" t="n">
         <v>7.771</v>
@@ -1715,7 +1715,7 @@
       </c>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="n">
-        <v>0.6856383098963399</v>
+        <v>0.6856383098963396</v>
       </c>
       <c r="E10" t="n">
         <v>7.6833</v>
@@ -1735,7 +1735,7 @@
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="n">
-        <v>0.679895154933163</v>
+        <v>0.6798951549331628</v>
       </c>
       <c r="E11" t="n">
         <v>5.8818</v>
@@ -1755,7 +1755,7 @@
       </c>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="n">
-        <v>0.6791674564727262</v>
+        <v>0.6791674564727265</v>
       </c>
       <c r="E12" t="n">
         <v>-0.8383</v>
@@ -1835,7 +1835,7 @@
       </c>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="n">
-        <v>0.6734037796373255</v>
+        <v>0.6734037796373257</v>
       </c>
       <c r="E16" t="n">
         <v>1.3919</v>
@@ -1855,7 +1855,7 @@
       </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="n">
-        <v>0.6675755482746746</v>
+        <v>0.6675755482746745</v>
       </c>
       <c r="E17" t="n">
         <v>0.8929</v>
@@ -2021,7 +2021,7 @@
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="n">
-        <v>0.7246050068889744</v>
+        <v>0.7246050068889742</v>
       </c>
       <c r="E3" t="n">
         <v>2.7042</v>
@@ -2101,7 +2101,7 @@
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="n">
-        <v>0.6944111271512234</v>
+        <v>0.6944111271512233</v>
       </c>
       <c r="E7" t="n">
         <v>5.9743</v>
@@ -2161,7 +2161,7 @@
       </c>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="n">
-        <v>0.6815230265954275</v>
+        <v>0.6815230265954274</v>
       </c>
       <c r="E10" t="n">
         <v>-3.4676</v>
@@ -2261,7 +2261,7 @@
       </c>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="n">
-        <v>0.6653901131054405</v>
+        <v>0.6653901131054404</v>
       </c>
       <c r="E15" t="n">
         <v>-2.2697</v>
@@ -2301,7 +2301,7 @@
       </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="n">
-        <v>0.6625201100552147</v>
+        <v>0.6625201100552145</v>
       </c>
       <c r="E17" t="n">
         <v>-1.0515</v>
@@ -2321,7 +2321,7 @@
       </c>
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="n">
-        <v>0.6614319896766522</v>
+        <v>0.6614319896766523</v>
       </c>
       <c r="E18" t="n">
         <v>-4.5343</v>
@@ -2487,7 +2487,7 @@
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="n">
-        <v>0.7204812658691668</v>
+        <v>0.7204812658691669</v>
       </c>
       <c r="E4" t="n">
         <v>-0.6823</v>
@@ -2507,7 +2507,7 @@
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="n">
-        <v>0.7170458823503409</v>
+        <v>0.7170458823503408</v>
       </c>
       <c r="E5" t="n">
         <v>5.7278</v>
@@ -2567,7 +2567,7 @@
       </c>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="n">
-        <v>0.6944565585637237</v>
+        <v>0.6944565585637236</v>
       </c>
       <c r="E8" t="n">
         <v>3.5</v>
@@ -2667,7 +2667,7 @@
       </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="n">
-        <v>0.6706934986155896</v>
+        <v>0.6706934986155898</v>
       </c>
       <c r="E13" t="n">
         <v>7.5286</v>
@@ -2747,7 +2747,7 @@
       </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="n">
-        <v>0.6569403811723989</v>
+        <v>0.6569403811723988</v>
       </c>
       <c r="E17" t="n">
         <v>4.1774</v>
@@ -2893,7 +2893,7 @@
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="n">
-        <v>0.7176055642200196</v>
+        <v>0.7176055642200199</v>
       </c>
       <c r="E2" t="n">
         <v>33.9015</v>
@@ -2913,7 +2913,7 @@
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="n">
-        <v>0.7138912974877671</v>
+        <v>0.7138912974877673</v>
       </c>
       <c r="E3" t="n">
         <v>0.5104</v>
@@ -2933,7 +2933,7 @@
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="n">
-        <v>0.7133153716439057</v>
+        <v>0.7133153716439058</v>
       </c>
       <c r="E4" t="n">
         <v>1.9169</v>
@@ -3133,7 +3133,7 @@
       </c>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="n">
-        <v>0.6814124588426835</v>
+        <v>0.6814124588426834</v>
       </c>
       <c r="E14" t="n">
         <v>5.3862</v>
@@ -3173,7 +3173,7 @@
       </c>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="n">
-        <v>0.6760887698859532</v>
+        <v>0.6760887698859531</v>
       </c>
       <c r="E16" t="n">
         <v>1.6172</v>
@@ -3193,7 +3193,7 @@
       </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="n">
-        <v>0.6613498531346752</v>
+        <v>0.6613498531346751</v>
       </c>
       <c r="E17" t="n">
         <v>0.7408</v>
@@ -3213,7 +3213,7 @@
       </c>
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="n">
-        <v>0.6570733568741679</v>
+        <v>0.6570733568741676</v>
       </c>
       <c r="E18" t="n">
         <v>-1.0246</v>
@@ -4054,7 +4054,7 @@
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="n">
-        <v>0.6798697679798188</v>
+        <v>0.6798697679798187</v>
       </c>
       <c r="E6" t="n">
         <v>21.2401</v>
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="n">
-        <v>0.6779730362005804</v>
+        <v>0.6779730362005805</v>
       </c>
       <c r="E7" t="n">
         <v>-0.4242</v>
@@ -4114,7 +4114,7 @@
       </c>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="n">
-        <v>0.6654096131077749</v>
+        <v>0.665409613107775</v>
       </c>
       <c r="E9" t="n">
         <v>11.2505</v>
@@ -4134,7 +4134,7 @@
       </c>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="n">
-        <v>0.6552388494269173</v>
+        <v>0.6552388494269172</v>
       </c>
       <c r="E10" t="n">
         <v>4.1601</v>
@@ -4154,7 +4154,7 @@
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="n">
-        <v>0.6548569443700161</v>
+        <v>0.654856944370016</v>
       </c>
       <c r="E11" t="n">
         <v>4.0462</v>
@@ -4314,7 +4314,7 @@
       </c>
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="n">
-        <v>0.6326125580117242</v>
+        <v>0.6326125580117243</v>
       </c>
       <c r="E19" t="n">
         <v>10.9175</v>
@@ -4420,7 +4420,7 @@
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="n">
-        <v>0.7040821243272046</v>
+        <v>0.7040821243272047</v>
       </c>
       <c r="E2" t="n">
         <v>2.4669</v>
@@ -4440,7 +4440,7 @@
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="n">
-        <v>0.6866577630591126</v>
+        <v>0.6866577630591125</v>
       </c>
       <c r="E3" t="n">
         <v>38.3065</v>
@@ -4720,7 +4720,7 @@
       </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="n">
-        <v>0.6267628139778244</v>
+        <v>0.6267628139778243</v>
       </c>
       <c r="E17" t="n">
         <v>-11.7154</v>
@@ -4740,7 +4740,7 @@
       </c>
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="n">
-        <v>0.6248748298440017</v>
+        <v>0.6248748298440018</v>
       </c>
       <c r="E18" t="n">
         <v>5.3394</v>
@@ -4926,7 +4926,7 @@
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="n">
-        <v>0.6940833616144634</v>
+        <v>0.6940833616144633</v>
       </c>
       <c r="E5" t="n">
         <v>2.9773</v>
@@ -4946,7 +4946,7 @@
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="n">
-        <v>0.6914557268233851</v>
+        <v>0.6914557268233853</v>
       </c>
       <c r="E6" t="n">
         <v>-5.1886</v>
@@ -5066,7 +5066,7 @@
       </c>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="n">
-        <v>0.651380614035201</v>
+        <v>0.6513806140352011</v>
       </c>
       <c r="E12" t="n">
         <v>-1.9056</v>
@@ -5106,7 +5106,7 @@
       </c>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="n">
-        <v>0.6483105966431377</v>
+        <v>0.6483105966431375</v>
       </c>
       <c r="E14" t="n">
         <v>3.1898</v>
@@ -5126,7 +5126,7 @@
       </c>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="n">
-        <v>0.6417239566283501</v>
+        <v>0.64172395662835</v>
       </c>
       <c r="E15" t="n">
         <v>4.952</v>
@@ -5372,7 +5372,7 @@
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="n">
-        <v>0.6365735191632348</v>
+        <v>0.6365735191632349</v>
       </c>
       <c r="E5" t="n">
         <v>-8.480600000000001</v>
@@ -5392,7 +5392,7 @@
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="n">
-        <v>0.6319572382210125</v>
+        <v>0.6319572382210126</v>
       </c>
       <c r="E6" t="n">
         <v>-0.6682</v>
@@ -5472,7 +5472,7 @@
       </c>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="n">
-        <v>0.6073876695898905</v>
+        <v>0.6073876695898907</v>
       </c>
       <c r="E10" t="n">
         <v>2.5784</v>
@@ -5532,7 +5532,7 @@
       </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="n">
-        <v>0.6016327875074283</v>
+        <v>0.6016327875074282</v>
       </c>
       <c r="E13" t="n">
         <v>1.964</v>
@@ -5672,7 +5672,7 @@
       </c>
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="n">
-        <v>0.591478016312611</v>
+        <v>0.5914780163126112</v>
       </c>
       <c r="E20" t="n">
         <v>-1.5368</v>
@@ -5778,7 +5778,7 @@
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="n">
-        <v>0.6903986078631413</v>
+        <v>0.6903986078631412</v>
       </c>
       <c r="E3" t="n">
         <v>-0.6925</v>
@@ -5918,7 +5918,7 @@
       </c>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="n">
-        <v>0.6633739327591168</v>
+        <v>0.6633739327591166</v>
       </c>
       <c r="E10" t="n">
         <v>3.1453</v>
@@ -5958,7 +5958,7 @@
       </c>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="n">
-        <v>0.6601250699587708</v>
+        <v>0.6601250699587707</v>
       </c>
       <c r="E12" t="n">
         <v>-1.5867</v>
@@ -6038,7 +6038,7 @@
       </c>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="n">
-        <v>0.6449072370248756</v>
+        <v>0.6449072370248754</v>
       </c>
       <c r="E16" t="n">
         <v>-0.5941</v>
@@ -6118,7 +6118,7 @@
       </c>
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="n">
-        <v>0.6337574457345559</v>
+        <v>0.6337574457345561</v>
       </c>
       <c r="E20" t="n">
         <v>-0.7415</v>
@@ -6204,7 +6204,7 @@
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="n">
-        <v>0.7293514701845994</v>
+        <v>0.7293514701845991</v>
       </c>
       <c r="E2" t="n">
         <v>-0.398</v>
@@ -6264,7 +6264,7 @@
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="n">
-        <v>0.6858376006561986</v>
+        <v>0.6858376006561984</v>
       </c>
       <c r="E5" t="n">
         <v>3.9569</v>
@@ -6284,7 +6284,7 @@
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="n">
-        <v>0.6798931704401915</v>
+        <v>0.6798931704401913</v>
       </c>
       <c r="E6" t="n">
         <v>7.4709</v>
@@ -6304,7 +6304,7 @@
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="n">
-        <v>0.6781738316735825</v>
+        <v>0.6781738316735823</v>
       </c>
       <c r="E7" t="n">
         <v>11.3978</v>
@@ -6344,7 +6344,7 @@
       </c>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="n">
-        <v>0.6752875576959567</v>
+        <v>0.6752875576959566</v>
       </c>
       <c r="E9" t="n">
         <v>-4.1667</v>
@@ -6404,7 +6404,7 @@
       </c>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="n">
-        <v>0.6607383237830176</v>
+        <v>0.6607383237830174</v>
       </c>
       <c r="E12" t="n">
         <v>-4.3495</v>
@@ -6444,7 +6444,7 @@
       </c>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="n">
-        <v>0.6559529761670025</v>
+        <v>0.6559529761670027</v>
       </c>
       <c r="E14" t="n">
         <v>4.9534</v>
@@ -6484,7 +6484,7 @@
       </c>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="n">
-        <v>0.6465423741729013</v>
+        <v>0.6465423741729016</v>
       </c>
       <c r="E16" t="n">
         <v>2.1279</v>
@@ -6504,7 +6504,7 @@
       </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="n">
-        <v>0.6436614707355449</v>
+        <v>0.643661470735545</v>
       </c>
       <c r="E17" t="n">
         <v>9.394399999999999</v>
@@ -6544,7 +6544,7 @@
       </c>
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="n">
-        <v>0.6335294946475944</v>
+        <v>0.6335294946475942</v>
       </c>
       <c r="E19" t="n">
         <v>1.9365</v>
@@ -6564,7 +6564,7 @@
       </c>
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="n">
-        <v>0.6333605972870847</v>
+        <v>0.6333605972870848</v>
       </c>
       <c r="E20" t="n">
         <v>2.5054</v>
@@ -6584,7 +6584,7 @@
       </c>
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="n">
-        <v>0.6332113548552342</v>
+        <v>0.6332113548552344</v>
       </c>
       <c r="E21" t="n">
         <v>2.2785</v>

--- a/results/reports/year_2025_report.xlsx
+++ b/results/reports/year_2025_report.xlsx
@@ -683,7 +683,7 @@
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="n">
-        <v>0.686230767247281</v>
+        <v>0.6862307672472809</v>
       </c>
       <c r="E3" t="n">
         <v>4.0767</v>
@@ -723,7 +723,7 @@
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="n">
-        <v>0.6701615958337335</v>
+        <v>0.6701615958337334</v>
       </c>
       <c r="E5" t="n">
         <v>1.8539</v>
@@ -763,7 +763,7 @@
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="n">
-        <v>0.6663407181068974</v>
+        <v>0.6663407181068977</v>
       </c>
       <c r="E7" t="n">
         <v>4.4389</v>
@@ -783,7 +783,7 @@
       </c>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="n">
-        <v>0.6646741675820408</v>
+        <v>0.6646741675820407</v>
       </c>
       <c r="E8" t="n">
         <v>-2.3659</v>
@@ -843,7 +843,7 @@
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="n">
-        <v>0.6523310838129955</v>
+        <v>0.6523310838129958</v>
       </c>
       <c r="E11" t="n">
         <v>1.8162</v>
@@ -903,7 +903,7 @@
       </c>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="n">
-        <v>0.6397480645383873</v>
+        <v>0.6397480645383874</v>
       </c>
       <c r="E14" t="n">
         <v>-4.0853</v>
@@ -923,7 +923,7 @@
       </c>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="n">
-        <v>0.6389839872772086</v>
+        <v>0.6389839872772085</v>
       </c>
       <c r="E15" t="n">
         <v>8.7927</v>
@@ -983,7 +983,7 @@
       </c>
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="n">
-        <v>0.6374203582290188</v>
+        <v>0.6374203582290189</v>
       </c>
       <c r="E18" t="n">
         <v>8.3926</v>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="n">
-        <v>0.6365870406856958</v>
+        <v>0.6365870406856959</v>
       </c>
       <c r="E19" t="n">
         <v>-0.4867</v>
@@ -1023,7 +1023,7 @@
       </c>
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="n">
-        <v>0.633416671816903</v>
+        <v>0.6334166718169029</v>
       </c>
       <c r="E20" t="n">
         <v>0.2552</v>
@@ -1043,7 +1043,7 @@
       </c>
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="n">
-        <v>0.6330345015291134</v>
+        <v>0.6330345015291133</v>
       </c>
       <c r="E21" t="n">
         <v>2.487</v>
@@ -1149,7 +1149,7 @@
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="n">
-        <v>0.6903016121227366</v>
+        <v>0.6903016121227367</v>
       </c>
       <c r="E4" t="n">
         <v>-0.9732</v>
@@ -1249,7 +1249,7 @@
       </c>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="n">
-        <v>0.6817809580811216</v>
+        <v>0.6817809580811215</v>
       </c>
       <c r="E9" t="n">
         <v>-0.7212</v>
@@ -1269,7 +1269,7 @@
       </c>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="n">
-        <v>0.6801230200758152</v>
+        <v>0.6801230200758149</v>
       </c>
       <c r="E10" t="n">
         <v>7.771</v>
@@ -1309,7 +1309,7 @@
       </c>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="n">
-        <v>0.675280109839774</v>
+        <v>0.6752801098397743</v>
       </c>
       <c r="E12" t="n">
         <v>1.4851</v>
@@ -1409,7 +1409,7 @@
       </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="n">
-        <v>0.6662441592969667</v>
+        <v>0.6662441592969668</v>
       </c>
       <c r="E17" t="n">
         <v>6.7254</v>
@@ -1489,7 +1489,7 @@
       </c>
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="n">
-        <v>0.6559874506210602</v>
+        <v>0.65598745062106</v>
       </c>
       <c r="E21" t="n">
         <v>-1.2773</v>
@@ -1555,7 +1555,7 @@
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="n">
-        <v>0.7233596613442391</v>
+        <v>0.723359661344239</v>
       </c>
       <c r="E2" t="n">
         <v>0.1975</v>
@@ -1715,7 +1715,7 @@
       </c>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="n">
-        <v>0.6856383098963396</v>
+        <v>0.6856383098963399</v>
       </c>
       <c r="E10" t="n">
         <v>7.6833</v>
@@ -1735,7 +1735,7 @@
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="n">
-        <v>0.6798951549331628</v>
+        <v>0.679895154933163</v>
       </c>
       <c r="E11" t="n">
         <v>5.8818</v>
@@ -1795,7 +1795,7 @@
       </c>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="n">
-        <v>0.6756697132843869</v>
+        <v>0.6756697132843867</v>
       </c>
       <c r="E14" t="n">
         <v>9.968500000000001</v>
@@ -2021,7 +2021,7 @@
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="n">
-        <v>0.7246050068889742</v>
+        <v>0.7246050068889744</v>
       </c>
       <c r="E3" t="n">
         <v>2.7042</v>
@@ -2041,7 +2041,7 @@
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="n">
-        <v>0.723363264041016</v>
+        <v>0.7233632640410158</v>
       </c>
       <c r="E4" t="n">
         <v>2.1298</v>
@@ -2121,7 +2121,7 @@
       </c>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="n">
-        <v>0.6900783392822956</v>
+        <v>0.6900783392822958</v>
       </c>
       <c r="E8" t="n">
         <v>2.3508</v>
@@ -2141,7 +2141,7 @@
       </c>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="n">
-        <v>0.6832619056728367</v>
+        <v>0.6832619056728368</v>
       </c>
       <c r="E9" t="n">
         <v>4.5358</v>
@@ -2161,7 +2161,7 @@
       </c>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="n">
-        <v>0.6815230265954274</v>
+        <v>0.6815230265954275</v>
       </c>
       <c r="E10" t="n">
         <v>-3.4676</v>
@@ -2301,7 +2301,7 @@
       </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="n">
-        <v>0.6625201100552145</v>
+        <v>0.6625201100552148</v>
       </c>
       <c r="E17" t="n">
         <v>-1.0515</v>
@@ -2361,7 +2361,7 @@
       </c>
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="n">
-        <v>0.65263205807132</v>
+        <v>0.6526320580713201</v>
       </c>
       <c r="E20" t="n">
         <v>7.4008</v>
@@ -2381,7 +2381,7 @@
       </c>
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="n">
-        <v>0.6518234010500279</v>
+        <v>0.6518234010500281</v>
       </c>
       <c r="E21" t="n">
         <v>-1.2091</v>
@@ -2467,7 +2467,7 @@
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="n">
-        <v>0.7320895150047403</v>
+        <v>0.7320895150047404</v>
       </c>
       <c r="E3" t="n">
         <v>3.2946</v>
@@ -2487,7 +2487,7 @@
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="n">
-        <v>0.7204812658691669</v>
+        <v>0.7204812658691671</v>
       </c>
       <c r="E4" t="n">
         <v>-0.6823</v>
@@ -2567,7 +2567,7 @@
       </c>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="n">
-        <v>0.6944565585637236</v>
+        <v>0.6944565585637237</v>
       </c>
       <c r="E8" t="n">
         <v>3.5</v>
@@ -2667,7 +2667,7 @@
       </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="n">
-        <v>0.6706934986155898</v>
+        <v>0.6706934986155896</v>
       </c>
       <c r="E13" t="n">
         <v>7.5286</v>
@@ -2727,7 +2727,7 @@
       </c>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="n">
-        <v>0.6573470477240523</v>
+        <v>0.6573470477240521</v>
       </c>
       <c r="E16" t="n">
         <v>2.1812</v>
@@ -2747,7 +2747,7 @@
       </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="n">
-        <v>0.6569403811723988</v>
+        <v>0.6569403811723989</v>
       </c>
       <c r="E17" t="n">
         <v>4.1774</v>
@@ -2767,7 +2767,7 @@
       </c>
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="n">
-        <v>0.6547390387261436</v>
+        <v>0.6547390387261437</v>
       </c>
       <c r="E18" t="n">
         <v>-0.0461</v>
@@ -2807,7 +2807,7 @@
       </c>
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="n">
-        <v>0.6541369925466815</v>
+        <v>0.6541369925466816</v>
       </c>
       <c r="E20" t="n">
         <v>13.3485</v>
@@ -2913,7 +2913,7 @@
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="n">
-        <v>0.7138912974877673</v>
+        <v>0.7138912974877671</v>
       </c>
       <c r="E3" t="n">
         <v>0.5104</v>
@@ -2933,7 +2933,7 @@
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="n">
-        <v>0.7133153716439058</v>
+        <v>0.7133153716439057</v>
       </c>
       <c r="E4" t="n">
         <v>1.9169</v>
@@ -3013,7 +3013,7 @@
       </c>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="n">
-        <v>0.6977040463317842</v>
+        <v>0.6977040463317843</v>
       </c>
       <c r="E8" t="n">
         <v>-1.1335</v>
@@ -3073,7 +3073,7 @@
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="n">
-        <v>0.6848484911963305</v>
+        <v>0.6848484911963304</v>
       </c>
       <c r="E11" t="n">
         <v>-0.0452</v>
@@ -3133,7 +3133,7 @@
       </c>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="n">
-        <v>0.6814124588426834</v>
+        <v>0.6814124588426835</v>
       </c>
       <c r="E14" t="n">
         <v>5.3862</v>
@@ -3153,7 +3153,7 @@
       </c>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="n">
-        <v>0.6797775055744271</v>
+        <v>0.6797775055744272</v>
       </c>
       <c r="E15" t="n">
         <v>9.993600000000001</v>
@@ -3173,7 +3173,7 @@
       </c>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="n">
-        <v>0.6760887698859531</v>
+        <v>0.6760887698859532</v>
       </c>
       <c r="E16" t="n">
         <v>1.6172</v>
@@ -3193,7 +3193,7 @@
       </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="n">
-        <v>0.6613498531346751</v>
+        <v>0.6613498531346752</v>
       </c>
       <c r="E17" t="n">
         <v>0.7408</v>
@@ -3233,7 +3233,7 @@
       </c>
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="n">
-        <v>0.6492901057438876</v>
+        <v>0.6492901057438875</v>
       </c>
       <c r="E19" t="n">
         <v>1.1494</v>
@@ -3994,7 +3994,7 @@
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="n">
-        <v>0.686948648062168</v>
+        <v>0.6869486480621678</v>
       </c>
       <c r="E3" t="n">
         <v>10.5786</v>
@@ -4034,7 +4034,7 @@
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="n">
-        <v>0.6820195257230013</v>
+        <v>0.6820195257230012</v>
       </c>
       <c r="E5" t="n">
         <v>2.0116</v>
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="n">
-        <v>0.6779730362005805</v>
+        <v>0.6779730362005804</v>
       </c>
       <c r="E7" t="n">
         <v>-0.4242</v>
@@ -4114,7 +4114,7 @@
       </c>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="n">
-        <v>0.665409613107775</v>
+        <v>0.6654096131077749</v>
       </c>
       <c r="E9" t="n">
         <v>11.2505</v>
@@ -4134,7 +4134,7 @@
       </c>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="n">
-        <v>0.6552388494269172</v>
+        <v>0.6552388494269173</v>
       </c>
       <c r="E10" t="n">
         <v>4.1601</v>
@@ -4174,7 +4174,7 @@
       </c>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="n">
-        <v>0.6505256667871633</v>
+        <v>0.6505256667871632</v>
       </c>
       <c r="E12" t="n">
         <v>16.6137</v>
@@ -4214,7 +4214,7 @@
       </c>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="n">
-        <v>0.6471948049488639</v>
+        <v>0.6471948049488642</v>
       </c>
       <c r="E14" t="n">
         <v>8.460900000000001</v>
@@ -4314,7 +4314,7 @@
       </c>
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="n">
-        <v>0.6326125580117243</v>
+        <v>0.6326125580117242</v>
       </c>
       <c r="E19" t="n">
         <v>10.9175</v>
@@ -4440,7 +4440,7 @@
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="n">
-        <v>0.6866577630591125</v>
+        <v>0.6866577630591126</v>
       </c>
       <c r="E3" t="n">
         <v>38.3065</v>
@@ -4500,7 +4500,7 @@
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="n">
-        <v>0.6594563669309034</v>
+        <v>0.6594563669309033</v>
       </c>
       <c r="E6" t="n">
         <v>6.9864</v>
@@ -4680,7 +4680,7 @@
       </c>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="n">
-        <v>0.6284749400519885</v>
+        <v>0.6284749400519883</v>
       </c>
       <c r="E15" t="n">
         <v>0.5991</v>
@@ -4720,7 +4720,7 @@
       </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="n">
-        <v>0.6267628139778243</v>
+        <v>0.6267628139778244</v>
       </c>
       <c r="E17" t="n">
         <v>-11.7154</v>
@@ -4906,7 +4906,7 @@
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="n">
-        <v>0.6958549347239205</v>
+        <v>0.6958549347239206</v>
       </c>
       <c r="E4" t="n">
         <v>-6.7427</v>
@@ -4926,7 +4926,7 @@
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="n">
-        <v>0.6940833616144633</v>
+        <v>0.6940833616144634</v>
       </c>
       <c r="E5" t="n">
         <v>2.9773</v>
@@ -4946,7 +4946,7 @@
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="n">
-        <v>0.6914557268233853</v>
+        <v>0.6914557268233851</v>
       </c>
       <c r="E6" t="n">
         <v>-5.1886</v>
@@ -4966,7 +4966,7 @@
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="n">
-        <v>0.6778711143295355</v>
+        <v>0.6778711143295354</v>
       </c>
       <c r="E7" t="n">
         <v>4.5638</v>
@@ -5026,7 +5026,7 @@
       </c>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="n">
-        <v>0.6589479529112865</v>
+        <v>0.6589479529112867</v>
       </c>
       <c r="E10" t="n">
         <v>1.7932</v>
@@ -5066,7 +5066,7 @@
       </c>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="n">
-        <v>0.6513806140352011</v>
+        <v>0.651380614035201</v>
       </c>
       <c r="E12" t="n">
         <v>-1.9056</v>
@@ -5086,7 +5086,7 @@
       </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="n">
-        <v>0.6505325204110863</v>
+        <v>0.6505325204110862</v>
       </c>
       <c r="E13" t="n">
         <v>0.9101</v>
@@ -5106,7 +5106,7 @@
       </c>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="n">
-        <v>0.6483105966431375</v>
+        <v>0.6483105966431377</v>
       </c>
       <c r="E14" t="n">
         <v>3.1898</v>
@@ -5166,7 +5166,7 @@
       </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="n">
-        <v>0.6403494486814018</v>
+        <v>0.6403494486814015</v>
       </c>
       <c r="E17" t="n">
         <v>6.0589</v>
@@ -5186,7 +5186,7 @@
       </c>
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="n">
-        <v>0.640166316365115</v>
+        <v>0.6401663163651152</v>
       </c>
       <c r="E18" t="n">
         <v>-9.056699999999999</v>
@@ -5226,7 +5226,7 @@
       </c>
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="n">
-        <v>0.637153423374622</v>
+        <v>0.6371534233746219</v>
       </c>
       <c r="E20" t="n">
         <v>-1.4619</v>
@@ -5246,7 +5246,7 @@
       </c>
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="n">
-        <v>0.6365310844682209</v>
+        <v>0.636531084468221</v>
       </c>
       <c r="E21" t="n">
         <v>-2.214</v>
@@ -5332,7 +5332,7 @@
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="n">
-        <v>0.6533953493539554</v>
+        <v>0.6533953493539555</v>
       </c>
       <c r="E3" t="n">
         <v>5.4789</v>
@@ -5452,7 +5452,7 @@
       </c>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="n">
-        <v>0.6096519750890582</v>
+        <v>0.6096519750890583</v>
       </c>
       <c r="E9" t="n">
         <v>8.4247</v>
@@ -5512,7 +5512,7 @@
       </c>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="n">
-        <v>0.6028857763693424</v>
+        <v>0.6028857763693425</v>
       </c>
       <c r="E12" t="n">
         <v>9.9664</v>
@@ -5532,7 +5532,7 @@
       </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="n">
-        <v>0.6016327875074282</v>
+        <v>0.6016327875074283</v>
       </c>
       <c r="E13" t="n">
         <v>1.964</v>
@@ -5572,7 +5572,7 @@
       </c>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="n">
-        <v>0.5996518492134711</v>
+        <v>0.5996518492134713</v>
       </c>
       <c r="E15" t="n">
         <v>3.757</v>
@@ -5672,7 +5672,7 @@
       </c>
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="n">
-        <v>0.5914780163126112</v>
+        <v>0.5914780163126111</v>
       </c>
       <c r="E20" t="n">
         <v>-1.5368</v>
@@ -5692,7 +5692,7 @@
       </c>
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="n">
-        <v>0.5877776682392739</v>
+        <v>0.587777668239274</v>
       </c>
       <c r="E21" t="n">
         <v>7.9252</v>
@@ -5778,7 +5778,7 @@
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="n">
-        <v>0.6903986078631412</v>
+        <v>0.6903986078631413</v>
       </c>
       <c r="E3" t="n">
         <v>-0.6925</v>
@@ -5798,7 +5798,7 @@
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="n">
-        <v>0.687847484300119</v>
+        <v>0.6878474843001189</v>
       </c>
       <c r="E4" t="n">
         <v>-5.6963</v>
@@ -5958,7 +5958,7 @@
       </c>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="n">
-        <v>0.6601250699587707</v>
+        <v>0.6601250699587708</v>
       </c>
       <c r="E12" t="n">
         <v>-1.5867</v>
@@ -6118,7 +6118,7 @@
       </c>
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="n">
-        <v>0.6337574457345561</v>
+        <v>0.6337574457345559</v>
       </c>
       <c r="E20" t="n">
         <v>-0.7415</v>
@@ -6264,7 +6264,7 @@
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="n">
-        <v>0.6858376006561984</v>
+        <v>0.6858376006561986</v>
       </c>
       <c r="E5" t="n">
         <v>3.9569</v>
@@ -6384,7 +6384,7 @@
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="n">
-        <v>0.6690311967477426</v>
+        <v>0.6690311967477425</v>
       </c>
       <c r="E11" t="n">
         <v>4.3963</v>
@@ -6444,7 +6444,7 @@
       </c>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="n">
-        <v>0.6559529761670027</v>
+        <v>0.6559529761670025</v>
       </c>
       <c r="E14" t="n">
         <v>4.9534</v>
@@ -6464,7 +6464,7 @@
       </c>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="n">
-        <v>0.654303027030759</v>
+        <v>0.6543030270307589</v>
       </c>
       <c r="E15" t="n">
         <v>3.7802</v>
@@ -6484,7 +6484,7 @@
       </c>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="n">
-        <v>0.6465423741729016</v>
+        <v>0.6465423741729015</v>
       </c>
       <c r="E16" t="n">
         <v>2.1279</v>
@@ -6524,7 +6524,7 @@
       </c>
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="n">
-        <v>0.6373749748082945</v>
+        <v>0.6373749748082946</v>
       </c>
       <c r="E18" t="n">
         <v>-1.7754</v>
@@ -6584,7 +6584,7 @@
       </c>
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="n">
-        <v>0.6332113548552344</v>
+        <v>0.6332113548552343</v>
       </c>
       <c r="E21" t="n">
         <v>2.2785</v>
